--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/18,08,26 Останкино СЫРЫ/дв 18,08,26 лгрсч ост сыр.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/18,08,26 Останкино СЫРЫ/дв 18,08,26 лгрсч ост сыр.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\18,08,26 Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3528B93-6CF9-457D-AEF8-3FC4B8CF56F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D333F545-0CFF-47DC-893A-CB1B439E66C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
